--- a/assets/docs/lop5/Hoat dong trai nghiem - Lop 5.xlsx
+++ b/assets/docs/lop5/Hoat dong trai nghiem - Lop 5.xlsx
@@ -1522,7 +1522,8 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB2a: HS làm và chia sẻ một sản phẩm số cho chủ đề.</t>
+          <t>Năng lực số 3.1 CB2a: HS làm và chia sẻ một sản phẩm số cho chủ đề.
+Học tập và làm theo Bác: Điều 5 “Khiêm tốn, thật thà, dũng cảm” (mạch 5): khi nêu vấn đề giữa thầy và trò, HS thật thà nói điều mình chưa hiểu, chưa làm được, mạnh dạn xin thầy cô giúp và biết nhận lỗi khi mình sai.</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1774,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1808,7 +1809,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -1843,7 +1844,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1878,7 +1879,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -1898,7 +1899,11 @@
           <t>40</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -1908,7 +1913,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -1942,7 +1947,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -1964,8 +1969,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1981,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -2011,7 +2015,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -2046,7 +2050,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -2068,8 +2072,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2084,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -2111,7 +2114,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -2146,7 +2149,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Quản lí chi tiêu và lập kế hoạch kinh doanh</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -2181,7 +2184,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -2211,7 +2214,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -2245,7 +2248,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -2280,7 +2283,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -2314,7 +2317,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -2349,7 +2352,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tôn sư trọng đạo</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -2384,7 +2387,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -2419,7 +2422,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -2453,7 +2456,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -2488,7 +2491,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -2522,7 +2525,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -2556,7 +2559,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình đầm ấm</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -2852,7 +2855,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
+          <t>Năng lực số 2.5 CB2a: HS chỉ ra được lời nhắn nào là tôn trọng, lời nhắn nào là trêu chọc, xúc phạm và chọn được cách trả lời phù hợp.
 KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
         </is>
       </c>
@@ -2887,7 +2890,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB2a: HS chỉ ra được lời nhắn nào là tôn trọng, lời nhắn nào là trêu chọc, xúc phạm và chọn được cách trả lời phù hợp.
+          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
 KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
         </is>
       </c>
@@ -3311,7 +3314,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -3346,7 +3349,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -3381,7 +3384,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -3404,7 +3407,7 @@
       <c r="H87" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục ý thức bảo vệ chủ quyền biển, đảo; trách nhiệm công dân trong xây dựng và bảo vệ Tổ quốc.</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3419,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -3450,7 +3453,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -3485,7 +3488,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -3520,7 +3523,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -3542,8 +3545,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhận biết cách ghi lại, sắp xếp số liệu khảo sát môi trường (lượng rác, cây xanh…) một cách đơn giản trên bảng số.
-QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục ý thức bảo vệ chủ quyền biển, đảo; trách nhiệm công dân trong xây dựng và bảo vệ Tổ quốc.</t>
+          <t>QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục ý thức bảo vệ chủ quyền biển, đảo; trách nhiệm công dân trong xây dựng và bảo vệ Tổ quốc.</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3557,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -3590,7 +3592,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -3625,7 +3627,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -3655,7 +3657,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -3690,7 +3692,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Tự hào quê hương em</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -3712,8 +3714,7 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3726,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -3760,7 +3761,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -3795,7 +3796,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -3830,7 +3831,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -3864,7 +3865,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -3899,7 +3900,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -3934,7 +3935,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -3954,7 +3955,11 @@
           <t>100</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr"/>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -3964,7 +3969,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -3999,7 +4004,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -4021,8 +4026,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4038,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -4056,8 +4060,7 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB2b: HS chọn cách lưu giữ kỉ niệm tiểu học bằng một sản phẩm số đơn giản (an-bum ảnh, đoạn trình chiếu).
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 3.1 CB2b: HS chọn cách lưu giữ kỉ niệm tiểu học bằng một sản phẩm số đơn giản (an-bum ảnh, đoạn trình chiếu).</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4072,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -4103,7 +4106,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Tham gia hoạt động xã hội</t>
+          <t>Chủ đề: Ước mơ nghề nghiệp</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
@@ -4125,8 +4128,7 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.</t>
         </is>
       </c>
     </row>
